--- a/docs/StructureDefinition-space-motion-sickness-condition.xlsx
+++ b/docs/StructureDefinition-space-motion-sickness-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-motion-sickness-condition.xlsx
+++ b/docs/StructureDefinition-space-motion-sickness-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-motion-sickness-condition</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-motion-sickness-condition</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -464,7 +467,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -484,7 +487,7 @@
     <t>gravityContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/gravity-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/gravity-context}
 </t>
   </si>
   <si>
@@ -500,7 +503,7 @@
     <t>flightDay</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://mitre.org/fhir/space-health/StructureDefinition/flight-day}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/flight-day}
 </t>
   </si>
   <si>
@@ -684,7 +687,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/graybiel-severity-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/graybiel-severity-vs</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -718,7 +721,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/space-motion-sickness-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/space-motion-sickness-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -785,7 +788,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1415,54 +1418,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1490,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1500,7 +1505,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="71.6640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.42578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.4140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1520,138 +1525,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1659,10 +1664,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1674,13 +1679,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1731,31 +1736,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -1766,10 +1771,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1777,10 +1782,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1789,19 +1794,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1851,13 +1856,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1886,10 +1891,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1897,10 +1902,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1909,16 +1914,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1969,19 +1974,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2004,10 +2009,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2015,31 +2020,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2089,19 +2094,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2124,10 +2129,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2135,10 +2140,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2150,16 +2155,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2185,13 +2190,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2209,19 +2214,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2244,21 +2249,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2270,16 +2275,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2329,19 +2334,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2353,7 +2358,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2364,21 +2369,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2390,16 +2395,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2449,13 +2454,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2473,7 +2478,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2484,10 +2489,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2495,10 +2500,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2510,13 +2515,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2555,29 +2560,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2600,26 +2605,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2628,13 +2633,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2685,19 +2690,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2720,26 +2725,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -2748,13 +2753,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2805,19 +2810,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2840,26 +2845,26 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2868,13 +2873,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2925,19 +2930,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2960,45 +2965,45 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3047,19 +3052,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -3071,7 +3076,7 @@
         <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3082,10 +3087,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3093,10 +3098,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3105,22 +3110,22 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3169,22 +3174,22 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3193,10 +3198,10 @@
         <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3204,10 +3209,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3215,31 +3220,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3265,13 +3270,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3289,34 +3294,34 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3324,10 +3329,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3335,31 +3340,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3385,13 +3390,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3409,45 +3414,45 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AG16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AP16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3455,10 +3460,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3470,16 +3475,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3505,13 +3510,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3529,34 +3534,34 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -3564,10 +3569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3575,13 +3580,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3590,16 +3595,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3625,11 +3630,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3647,78 +3652,78 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3743,11 +3748,11 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3765,45 +3770,45 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3811,10 +3816,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3823,19 +3828,19 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3861,13 +3866,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3885,78 +3890,78 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4005,34 +4010,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4040,10 +4045,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4051,10 +4056,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4063,19 +4068,19 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4125,34 +4130,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4160,10 +4165,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4171,31 +4176,31 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4245,34 +4250,34 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4280,10 +4285,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4291,13 +4296,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4306,16 +4311,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4365,19 +4370,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4389,10 +4394,10 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4400,10 +4405,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4411,10 +4416,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4423,16 +4428,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4483,19 +4488,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4504,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4518,10 +4523,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4529,10 +4534,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4541,16 +4546,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4601,19 +4606,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4625,10 +4630,10 @@
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -4636,10 +4641,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4647,10 +4652,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4659,16 +4664,16 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4719,19 +4724,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4740,13 +4745,13 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -4754,10 +4759,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4765,13 +4770,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -4780,13 +4785,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4837,19 +4842,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4861,7 +4866,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4872,10 +4877,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4883,10 +4888,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4898,13 +4903,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4955,13 +4960,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -4979,7 +4984,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4990,21 +4995,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5016,16 +5021,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5075,19 +5080,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5099,7 +5104,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5110,45 +5115,45 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5197,19 +5202,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5221,7 +5226,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5232,10 +5237,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5243,10 +5248,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5258,13 +5263,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5291,13 +5296,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5315,31 +5320,31 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5361,10 +5366,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5376,13 +5381,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5433,19 +5438,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5457,7 +5462,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5468,10 +5473,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5479,10 +5484,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5494,13 +5499,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5527,13 +5532,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5551,19 +5556,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5575,7 +5580,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5586,10 +5591,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5597,10 +5602,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5612,16 +5617,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5671,19 +5676,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5695,7 +5700,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5706,10 +5711,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5717,10 +5722,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5732,13 +5737,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5789,13 +5794,13 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -5813,7 +5818,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5824,21 +5829,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5850,16 +5855,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5909,19 +5914,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5933,7 +5938,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5944,45 +5949,45 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6031,19 +6036,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6055,7 +6060,7 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6066,10 +6071,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6077,10 +6082,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6089,16 +6094,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6125,13 +6130,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6149,34 +6154,34 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -6184,10 +6189,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6195,10 +6200,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6207,16 +6212,16 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6267,34 +6272,34 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -6302,10 +6307,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6313,10 +6318,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6328,13 +6333,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6385,31 +6390,31 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
